--- a/cet4/result/68_革命女神_巾帼英雄的传奇路/68_革命女神_巾帼英雄的传奇路_学习版.xlsx
+++ b/cet4/result/68_革命女神_巾帼英雄的传奇路/68_革命女神_巾帼英雄的传奇路_学习版.xlsx
@@ -397,857 +397,675 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D47"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>unknown</v>
       </c>
       <c r="B2" t="str">
-        <v>unknown</v>
+        <v>/ˌʌnˈnoʊn/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>未知</v>
       </c>
-      <c r="D2" t="str">
-        <v>unknown(未知)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>thirteen</v>
       </c>
       <c r="B3" t="str">
-        <v>thirteen</v>
+        <v>/ˌθɜːrˈtiːn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D3" t="str">
         <v>十三</v>
       </c>
-      <c r="D3" t="str">
-        <v>thirteen(十三)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>male</v>
       </c>
       <c r="B4" t="str">
-        <v>male</v>
+        <v>/meɪl/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>男性</v>
       </c>
-      <c r="D4" t="str">
-        <v>male(男性)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>constant</v>
       </c>
       <c r="B5" t="str">
-        <v>constant</v>
+        <v>/ˈkɑːnstənt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>恒定</v>
       </c>
-      <c r="D5" t="str">
-        <v>constant(恒定)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>today</v>
       </c>
       <c r="B6" t="str">
-        <v>today</v>
+        <v>/təˈdeɪ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D6" t="str">
         <v>今天</v>
       </c>
-      <c r="D6" t="str">
-        <v>today(今天)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>normal</v>
       </c>
       <c r="B7" t="str">
-        <v>normal</v>
+        <v>/ˈnɔːrml/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>正常</v>
       </c>
-      <c r="D7" t="str">
-        <v>normal(正常)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>meeting</v>
       </c>
       <c r="B8" t="str">
-        <v>meeting</v>
+        <v>/ˈmiːtɪŋ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>会议</v>
       </c>
-      <c r="D8" t="str">
-        <v>meeting(会议)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>electrical</v>
       </c>
       <c r="B9" t="str">
-        <v>electrical</v>
+        <v>/ɪˈlektrɪkl/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>电气的</v>
       </c>
-      <c r="D9" t="str">
-        <v>electrical(电气的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>explore</v>
       </c>
       <c r="B10" t="str">
-        <v>explore</v>
+        <v>/ɪkˈsplɔːr/</v>
       </c>
       <c r="C10" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>探索</v>
       </c>
-      <c r="D10" t="str">
-        <v>explore(探索)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>miracle</v>
       </c>
       <c r="B11" t="str">
-        <v>miracle</v>
+        <v>/ˈmɪrəkl/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>奇迹</v>
       </c>
-      <c r="D11" t="str">
-        <v>miracle(奇迹)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>fortnight</v>
       </c>
       <c r="B12" t="str">
-        <v>fortnight</v>
+        <v>/ˈfɔːrtnaɪt/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>两星期</v>
       </c>
-      <c r="D12" t="str">
-        <v>fortnight(两星期)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>stocking</v>
       </c>
       <c r="B13" t="str">
-        <v>stocking</v>
+        <v>/ˈstɑːkɪŋ/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>长袜</v>
       </c>
-      <c r="D13" t="str">
-        <v>stocking(长袜)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>equality</v>
       </c>
       <c r="B14" t="str">
-        <v>equality</v>
+        <v>/iˈkwɑːləti/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>平等</v>
       </c>
-      <c r="D14" t="str">
-        <v>equality(平等)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>general</v>
       </c>
       <c r="B15" t="str">
-        <v>general</v>
+        <v>/ˈdʒenrəl/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>一般</v>
       </c>
-      <c r="D15" t="str">
-        <v>general(一般)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>navigation</v>
       </c>
       <c r="B16" t="str">
-        <v>electrical</v>
+        <v>/ˌnævɪˈɡeɪʃn/</v>
       </c>
       <c r="C16" t="str">
-        <v>电气的</v>
+        <v>n.</v>
       </c>
       <c r="D16" t="str">
-        <v>electrical(电气的)📢</v>
+        <v>航行</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>exert</v>
       </c>
       <c r="B17" t="str">
-        <v>navigation</v>
+        <v>/ɪɡˈzɜːrt/</v>
       </c>
       <c r="C17" t="str">
-        <v>航行</v>
+        <v>vt.</v>
       </c>
       <c r="D17" t="str">
-        <v>navigation(航行)📢</v>
+        <v>运用</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>France</v>
       </c>
       <c r="B18" t="str">
-        <v>exert</v>
+        <v>/fræns/</v>
       </c>
       <c r="C18" t="str">
-        <v>运用</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>exert(运用)📢</v>
+        <v>法国</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>three</v>
       </c>
       <c r="B19" t="str">
-        <v>France</v>
+        <v>/θriː/</v>
       </c>
       <c r="C19" t="str">
-        <v>法国</v>
+        <v>n./adj./num.</v>
       </c>
       <c r="D19" t="str">
-        <v>France(法国)📢</v>
+        <v>三</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>everyone</v>
       </c>
       <c r="B20" t="str">
-        <v>three</v>
+        <v>/ˈevriwʌn/</v>
       </c>
       <c r="C20" t="str">
-        <v>三</v>
+        <v>n./pron.</v>
       </c>
       <c r="D20" t="str">
-        <v>three(三)📢</v>
+        <v>每个人</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>tragedy</v>
       </c>
       <c r="B21" t="str">
-        <v>equality</v>
+        <v>/ˈtrædʒədi/</v>
       </c>
       <c r="C21" t="str">
-        <v>平等</v>
+        <v>n.</v>
       </c>
       <c r="D21" t="str">
-        <v>equality(平等)📢</v>
+        <v>悲剧</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>inform</v>
       </c>
       <c r="B22" t="str">
-        <v>everyone</v>
+        <v>/ɪnˈfɔːrm/</v>
       </c>
       <c r="C22" t="str">
-        <v>每个人</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D22" t="str">
-        <v>everyone(每个人)📢</v>
+        <v>通知</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>yet</v>
       </c>
       <c r="B23" t="str">
-        <v>tragedy</v>
+        <v>/jet/</v>
       </c>
       <c r="C23" t="str">
-        <v>悲剧</v>
+        <v>n./v./adv./conj.</v>
       </c>
       <c r="D23" t="str">
-        <v>tragedy(悲剧)📢</v>
+        <v>还</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>implication</v>
       </c>
       <c r="B24" t="str">
-        <v>electrical</v>
+        <v>/ˌɪmplɪˈkeɪʃn/</v>
       </c>
       <c r="C24" t="str">
-        <v>电气的</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>electrical(电气的)📢</v>
+        <v>牵连</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>depend</v>
       </c>
       <c r="B25" t="str">
-        <v>inform</v>
+        <v>/dɪˈpend/</v>
       </c>
       <c r="C25" t="str">
-        <v>通知</v>
+        <v>vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>inform(通知)📢</v>
+        <v>依靠</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>list</v>
       </c>
       <c r="B26" t="str">
-        <v>yet</v>
+        <v>/lɪst/</v>
       </c>
       <c r="C26" t="str">
-        <v>还</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>yet(还)📢</v>
+        <v>名单</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>native</v>
       </c>
       <c r="B27" t="str">
-        <v>implication</v>
+        <v>/ˈneɪtɪv/</v>
       </c>
       <c r="C27" t="str">
-        <v>牵连</v>
+        <v>n./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>implication(牵连)📢</v>
+        <v>本地</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>vice</v>
       </c>
       <c r="B28" t="str">
-        <v>depend</v>
+        <v>/vaɪs/</v>
       </c>
       <c r="C28" t="str">
-        <v>依靠</v>
+        <v>n./vt./adj./prep.</v>
       </c>
       <c r="D28" t="str">
-        <v>depend(依靠)📢</v>
+        <v>副</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>wool</v>
       </c>
       <c r="B29" t="str">
-        <v>list</v>
+        <v>/wʊl/</v>
       </c>
       <c r="C29" t="str">
-        <v>名单</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>list(名单)📢</v>
+        <v>羊毛</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>bell</v>
       </c>
       <c r="B30" t="str">
-        <v>native</v>
+        <v>/bel/</v>
       </c>
       <c r="C30" t="str">
-        <v>本地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>native(本地)📢</v>
+        <v>钟声</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>additional</v>
       </c>
       <c r="B31" t="str">
-        <v>vice</v>
+        <v>/əˈdɪʃənl/</v>
       </c>
       <c r="C31" t="str">
-        <v>副</v>
+        <v>adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>vice(副)📢</v>
+        <v>额外的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>plot</v>
       </c>
       <c r="B32" t="str">
-        <v>wool</v>
+        <v>/plɑːt/</v>
       </c>
       <c r="C32" t="str">
-        <v>羊毛</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>wool(羊毛)📢</v>
+        <v>密谋</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>orbit</v>
       </c>
       <c r="B33" t="str">
-        <v>bell</v>
+        <v>/ˈɔːrbɪt/</v>
       </c>
       <c r="C33" t="str">
-        <v>钟声</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>bell(钟声)📢</v>
+        <v>轨道</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>treason</v>
       </c>
       <c r="B34" t="str">
-        <v>additional</v>
+        <v>/ˈtriːzn/</v>
       </c>
       <c r="C34" t="str">
-        <v>额外的</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>additional(额外的)📢</v>
+        <v>叛国</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>gunpowder</v>
       </c>
       <c r="B35" t="str">
-        <v>plot</v>
+        <v>/ˈɡʌnpaʊdər/</v>
       </c>
       <c r="C35" t="str">
-        <v>密谋</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>plot(密谋)📢</v>
+        <v>火药</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>fix</v>
       </c>
       <c r="B36" t="str">
-        <v>orbit</v>
+        <v>/fɪks/</v>
       </c>
       <c r="C36" t="str">
-        <v>轨道</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>orbit(轨道)📢</v>
+        <v>固定</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>strain</v>
       </c>
       <c r="B37" t="str">
-        <v>treason</v>
+        <v>/streɪn/</v>
       </c>
       <c r="C37" t="str">
-        <v>叛国</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>treason(叛国)📢</v>
+        <v>拉紧</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>jet</v>
       </c>
       <c r="B38" t="str">
-        <v>yet</v>
+        <v>/dʒet/</v>
       </c>
       <c r="C38" t="str">
-        <v>然而</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D38" t="str">
-        <v>yet(然而)📢</v>
+        <v>喷气式飞机</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>refine</v>
       </c>
       <c r="B39" t="str">
-        <v>miracle</v>
+        <v>/rɪˈfaɪn/</v>
       </c>
       <c r="C39" t="str">
-        <v>奇迹</v>
+        <v>vt.</v>
       </c>
       <c r="D39" t="str">
-        <v>miracle(奇迹)📢</v>
+        <v>精炼</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>consistent</v>
       </c>
       <c r="B40" t="str">
-        <v>gunpowder</v>
+        <v>/kənˈsɪstənt/</v>
       </c>
       <c r="C40" t="str">
-        <v>火药</v>
+        <v>adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>gunpowder(火药)📢</v>
+        <v>始终如一</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>alternative</v>
       </c>
       <c r="B41" t="str">
-        <v>three</v>
+        <v>/ɔːlˈtɜːrnətɪv/</v>
       </c>
       <c r="C41" t="str">
-        <v>三</v>
+        <v>n./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>three(三)📢</v>
+        <v>二选一</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>traditional</v>
       </c>
       <c r="B42" t="str">
-        <v>fix</v>
+        <v>/trəˈdɪʃənl/</v>
       </c>
       <c r="C42" t="str">
-        <v>固定</v>
+        <v>adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>fix(固定)📢</v>
+        <v>传统</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>curl</v>
       </c>
       <c r="B43" t="str">
-        <v>strain</v>
+        <v>/kɜːrl/</v>
       </c>
       <c r="C43" t="str">
-        <v>拉紧</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>strain(拉紧)📢</v>
+        <v>卷曲</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>cut</v>
       </c>
       <c r="B44" t="str">
-        <v>jet</v>
+        <v>/kʌt/</v>
       </c>
       <c r="C44" t="str">
-        <v>喷气式飞机</v>
+        <v>n./v.</v>
       </c>
       <c r="D44" t="str">
-        <v>jet(喷气式飞机)📢</v>
+        <v>切断</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>illustration</v>
       </c>
       <c r="B45" t="str">
-        <v>refine</v>
+        <v>/ˌɪləˈstreɪʃn/</v>
       </c>
       <c r="C45" t="str">
-        <v>精炼</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>refine(精炼)📢</v>
+        <v>插图</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>glimpse</v>
       </c>
       <c r="B46" t="str">
-        <v>equality</v>
+        <v>/ɡlɪmps/</v>
       </c>
       <c r="C46" t="str">
-        <v>平等</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>equality(平等)📢</v>
+        <v>一瞥</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>duck</v>
       </c>
       <c r="B47" t="str">
-        <v>consistent</v>
+        <v>/dʌk/</v>
       </c>
       <c r="C47" t="str">
-        <v>始终如一</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>consistent(始终如一)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>alternative</v>
-      </c>
-      <c r="C48" t="str">
-        <v>二选一</v>
-      </c>
-      <c r="D48" t="str">
-        <v>alternative(二选一)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>traditional</v>
-      </c>
-      <c r="C49" t="str">
-        <v>传统</v>
-      </c>
-      <c r="D49" t="str">
-        <v>traditional(传统)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>wool</v>
-      </c>
-      <c r="C50" t="str">
-        <v>羊毛</v>
-      </c>
-      <c r="D50" t="str">
-        <v>wool(羊毛)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>curl</v>
-      </c>
-      <c r="C51" t="str">
-        <v>卷曲</v>
-      </c>
-      <c r="D51" t="str">
-        <v>curl(卷曲)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>cut</v>
-      </c>
-      <c r="C52" t="str">
-        <v>切断</v>
-      </c>
-      <c r="D52" t="str">
-        <v>cut(切断)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>bell</v>
-      </c>
-      <c r="C53" t="str">
-        <v>钟楼</v>
-      </c>
-      <c r="D53" t="str">
-        <v>bell(钟楼)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>yet</v>
-      </c>
-      <c r="C54" t="str">
-        <v>仍然</v>
-      </c>
-      <c r="D54" t="str">
-        <v>yet(仍然)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>exert</v>
-      </c>
-      <c r="C55" t="str">
-        <v>付出</v>
-      </c>
-      <c r="D55" t="str">
-        <v>exert(付出)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>illustration</v>
-      </c>
-      <c r="C56" t="str">
-        <v>插图</v>
-      </c>
-      <c r="D56" t="str">
-        <v>illustration(插图)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>glimpse</v>
-      </c>
-      <c r="C57" t="str">
-        <v>一瞥</v>
-      </c>
-      <c r="D57" t="str">
-        <v>glimpse(一瞥)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>duck</v>
-      </c>
-      <c r="C58" t="str">
         <v>鸭子</v>
-      </c>
-      <c r="D58" t="str">
-        <v>duck(鸭子)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>miracle</v>
-      </c>
-      <c r="C59" t="str">
-        <v>奇迹</v>
-      </c>
-      <c r="D59" t="str">
-        <v>miracle(奇迹)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>France</v>
-      </c>
-      <c r="C60" t="str">
-        <v>法国</v>
-      </c>
-      <c r="D60" t="str">
-        <v>France(法国)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D47"/>
   </ignoredErrors>
 </worksheet>
 </file>